--- a/selenium_model/MASTER_TEST_AUDIT_REPORT.xlsx
+++ b/selenium_model/MASTER_TEST_AUDIT_REPORT.xlsx
@@ -14,17 +14,18 @@
     <sheet name="06 Performance Tests" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="07 Load Test Results" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="08 Vulnerability Tests" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="09 E2E Flow Tests" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="10 Functional Coverage" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="11 Defect Report" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="12 Security Observations" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="13 Accessibility Findings" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="14 Unused Files" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="15 Dead Code" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="16 Code Health" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="17 Recommendations" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="18 Navigation Coverage" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="19 Execution Summary" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="09 Appium Mobile Tests" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="10 E2E Flow Tests" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="11 Functional Coverage" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="12 Defect Report" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="13 Security Observations" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="14 Accessibility Findings" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="15 Unused Files" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="16 Dead Code" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="17 Code Health" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="18 Recommendations" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="19 Navigation Coverage" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="20 Execution Summary" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -48,7 +49,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -92,6 +93,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
@@ -124,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,6 +163,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -551,7 +560,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03 00:19:09</t>
+          <t>2026-08-03 00:24:01</t>
         </is>
       </c>
     </row>
@@ -873,6 +882,938 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="70" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Test #</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Test ID</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Duration (s)</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Screenshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>tests/test_e2e_flows.py::test_e2e_001_full_onboarding_skip_path</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>E2E Flow</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Selenium</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>E2E-001: Full onboarding Skip path: Welcome → Get Started → Skip → RegisterScreen</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>RegisterScreen visible at end of flow</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>RegisterScreen reached via Welcome → Get Started → Skip</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:37:36</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\91637\VoxiraApp\selenium_model\reports\screenshots\passed\test_e2e_001_full_onboarding_skip_path_1785564455943.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>tests/test_e2e_flows.py::test_e2e_002_sign_in_flow_welcome_to_login</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>E2E Flow</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Selenium</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>E2E-002: Sign In flow: Welcome → Sign In → LoginScreen</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>LoginScreen 'Welcome Back' visible</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>LoginScreen rendered via Welcome → Sign In</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>4.276</v>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:37:45</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\91637\VoxiraApp\selenium_model\reports\screenshots\passed\test_e2e_002_sign_in_flow_welcome_to_login_1785564465178.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>tests/test_e2e_flows.py::test_e2e_003_navigate_to_forgot_password_and_back</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>E2E Flow</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Selenium</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>E2E-003: Welcome → Login → Forgot Password → Return to Login</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>LoginScreen visible at end of chain</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Full round-trip navigation chain completed</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>6.292</v>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:37:56</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\91637\VoxiraApp\selenium_model\reports\screenshots\passed\test_e2e_003_navigate_to_forgot_password_and_back_1785564476395.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>tests/test_e2e_flows.py::test_e2e_004_register_to_login_crosslink</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>E2E Flow</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Selenium</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>E2E-004: Register → Sign In link → LoginScreen</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>LoginScreen visible after clicking Sign In from Register</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>LoginScreen reached from RegisterScreen Sign In link</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>23.548</v>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:38:27</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\91637\VoxiraApp\selenium_model\reports\screenshots\passed\test_e2e_004_register_to_login_crosslink_1785564506901.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>tests/test_e2e_flows.py::test_e2e_005_validation_chain_register</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>E2E Flow</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Selenium</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>E2E-005: Register with bad data → validation errors → fix data → errors clear</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Validation errors shown, then cleared after correction</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>bad_calls=0, errors_cleared=True</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>33.696</v>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:39:18</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\91637\VoxiraApp\selenium_model\reports\screenshots\passed\test_e2e_005_validation_chain_register_1785564557933.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>tests/test_e2e_flows.py::test_e2e_006_forgot_password_valid_submission</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>E2E Flow</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Selenium</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>E2E-006: ForgotPassword with valid email format fires recover call</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>≥1 call to /auth/v1/recover after submitting valid email</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>recover_calls=1</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>8.621</v>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:39:31</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\91637\VoxiraApp\selenium_model\reports\screenshots\passed\test_e2e_006_forgot_password_valid_submission_1785564571485.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>tests/test_e2e_flows.py::test_e2e_007_multiple_xss_payloads_all_blocked</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>E2E Flow</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Selenium</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>E2E-007: All 5 XSS payloads in Login email field are blocked (no alert, 0 calls)</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>0 alerts, 0 auth calls across all payloads</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>alerts=0, network_calls=0</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>87.117</v>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:41:04</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\91637\VoxiraApp\selenium_model\reports\screenshots\passed\test_e2e_007_multiple_xss_payloads_all_blocked_1785564663997.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>tests/test_e2e_flows.py::test_e2e_008_onboarding_no_errors_throughout</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>E2E Flow</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Selenium</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>E2E-008: Full onboarding (Welcome→Carousel→Skip→Register) has 0 JS SEVERE errors</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>0 SEVERE console entries across all screens</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>0 SEVERE errors</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>6.267</v>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:41:15</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\91637\VoxiraApp\selenium_model\reports\screenshots\passed\test_e2e_008_onboarding_no_errors_throughout_1785564675162.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>tests/test_e2e_flows.py::test_e2e_009_login_invalid_then_forgot_password</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>E2E Flow</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Selenium</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>E2E-009: Failed login → click Forgot Password → send reset → Return to Login</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>LoginScreen visible at end; total auth calls = 1 (invalid login attempt)</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Full login→forgot_password→return flow completed</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>28.85</v>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:41:47</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\91637\VoxiraApp\selenium_model\reports\screenshots\passed\test_e2e_009_login_invalid_then_forgot_password_1785564707772.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>tests/test_e2e_flows.py::test_e2e_010_register_all_invalid_fields_one_by_one</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>E2E Flow</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Selenium</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>E2E-010: Fix register fields one by one — 0 signup calls until all valid</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>0 calls while any field invalid; call only when all valid (submit NOT clicked for final)</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Stepped through field corrections; 0 calls until all valid</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>11.156</v>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:42:04</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\91637\VoxiraApp\selenium_model\reports\screenshots\passed\test_e2e_010_register_all_invalid_fields_one_by_one_1785564724135.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>tests/test_e2e_flows.py::test_e2e_011_back_navigation_consistency</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>E2E Flow</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Selenium</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>E2E-011: Navigating to BASE_URL always returns to WelcomeScreen (SPA routing)</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>WelcomeScreen visible when loading BASE_URL directly</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>WelcomeScreen confirmed after direct BASE_URL navigation (SPA pattern)</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>7.803</v>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:42:16</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\91637\VoxiraApp\selenium_model\reports\screenshots\passed\test_e2e_011_back_navigation_consistency_1785564736748.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>tests/test_e2e_flows.py::test_e2e_012_page_reload_returns_to_welcome</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>E2E Flow</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Selenium</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>E2E-012: Hard-refreshing the page always renders WelcomeScreen (no URL routing)</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>WelcomeScreen visible after driver.refresh() on any screen</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>WelcomeScreen shown after hard refresh</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:42:28</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\91637\VoxiraApp\selenium_model\reports\screenshots\passed\test_e2e_012_page_reload_returns_to_welcome_1785564748819.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>tests/test_e2e_flows.py::test_e2e_013_three_failed_logins_no_lockout_ui</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>E2E Flow</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Selenium</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>E2E-013: 3 consecutive failed login attempts — app stays functional (no client lockout)</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>LoginScreen still interactive after 3 failures</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>LoginScreen remains interactive after 3 failed attempts</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>62.15</v>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:43:34</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\91637\VoxiraApp\selenium_model\reports\screenshots\passed\test_e2e_013_three_failed_logins_no_lockout_ui_1785564814478.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>tests/test_e2e_flows.py::test_e2e_014_register_form_clears_on_navigate_away</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>E2E Flow</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Selenium</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>E2E-014: Register → Login → Register again — form state is reset</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>RegisterScreen has empty fields on second visit (no stale state)</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>name_field_value=''</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>40.141</v>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:44:19</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\91637\VoxiraApp\selenium_model\reports\screenshots\passed\test_e2e_014_register_form_clears_on_navigate_away_1785564859743.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>tests/test_e2e_flows.py::test_e2e_015_network_requests_stable_after_failed_login</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>E2E Flow</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Selenium</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>E2E-015: After failed login, no retry storm — call count stays at 1 for 5 seconds</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>auth call count doesn't grow after initial 1 call</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>calls_4s=0, calls_7s=0</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>28.171</v>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:44:52</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\91637\VoxiraApp\selenium_model\reports\screenshots\passed\test_e2e_015_network_requests_stable_after_failed_login_1785564892613.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>tests/test_e2e_flows.py::test_e2e_016_tab_bar_shown_only_when_authenticated</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>E2E Flow</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Selenium</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>E2E-016: Tab bar is NOT visible on unauthenticated screens</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Home/Speech/Profile tabs absent on WelcomeScreen and LoginScreen</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>tabs_on_welcome=False, tabs_on_login=False</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>20.083</v>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:45:17</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\91637\VoxiraApp\selenium_model\reports\screenshots\passed\test_e2e_016_tab_bar_shown_only_when_authenticated_1785564917461.png</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -970,81 +1911,81 @@
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>GoalSelectionScreen</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Multi-select onboarding goals, saved to Supabase</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Not Covered</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>src/screens/onboarding/GoalSelectionScreen.tsx</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>Requires authenticated session or Appium device</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>ExperienceLevelScreen</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Single-select skill level, saved to Supabase</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Not Covered</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>src/screens/onboarding/ExperienceLevelScreen.tsx</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>Requires authenticated session or Appium device</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>PermissionsScreen</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Mic/notification permission requests</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>Not Covered</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>src/screens/onboarding/PermissionsScreen.tsx</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>Requires authenticated session or Appium device</t>
         </is>
@@ -1132,108 +2073,108 @@
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>DeleteAccountScreen</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Multi-step account deletion wizard</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>Not Covered</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>src/screens/auth/DeleteAccountScreen.tsx</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>Requires authenticated session or Appium device</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>DashboardScreen</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>Stat cards, recent sessions, pull-to-refresh</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>Not Covered</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>src/screens/home/DashboardScreen.tsx</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>Requires authenticated session or Appium device</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>SearchScreen</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Client-side text+category filter (static array)</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>Not Covered</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>src/screens/home/SearchScreen.tsx</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>Requires authenticated session or Appium device</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>DailyGoalScreen</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>Stepper form for daily speech target + reminders</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>Not Covered</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>src/screens/home/DailyGoalScreen.tsx</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="10" t="inlineStr">
         <is>
           <t>Requires authenticated session or Appium device</t>
         </is>
@@ -1267,27 +2208,27 @@
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>TopicDetailScreen</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>Static topic content viewer</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>Not Covered</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>src/screens/home/TopicDetailScreen.tsx</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>Requires authenticated session or Appium device</t>
         </is>
@@ -1321,81 +2262,81 @@
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>EditProfileScreen</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>Profile form + avatar upload to Supabase Storage</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>Not Covered</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>src/screens/profile/EditProfileScreen.tsx</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>Requires authenticated session or Appium device</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>ProgressOverviewScreen</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>Stat aggregation from session history</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>Not Covered</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>src/screens/profile/ProgressOverviewScreen.tsx</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t>Requires authenticated session or Appium device</t>
         </is>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>AchievementsScreen</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>12 hardcoded achievements evaluated against real session data</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>Not Covered</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>src/screens/profile/AchievementsScreen.tsx</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E19" s="10" t="inlineStr">
         <is>
           <t>Requires authenticated session or Appium device</t>
         </is>
@@ -1429,54 +2370,54 @@
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>NotificationSettingsScreen</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>6 notification toggles + reminder time</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>Not Covered</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>src/screens/settings/NotificationSettingsScreen.tsx</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E21" s="10" t="inlineStr">
         <is>
           <t>Requires authenticated session or Appium device</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>PrivacyPolicyScreen</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>Static accordion content</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>Not Covered</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>src/screens/settings/PrivacyPolicyScreen.tsx</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E22" s="10" t="inlineStr">
         <is>
           <t>Requires authenticated session or Appium device</t>
         </is>
@@ -1510,27 +2451,27 @@
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>FAQScreen / TutorialScreen / WhatsNewScreen</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>Static support content</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>Not Covered</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t>src/screens/support/</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="E24" s="10" t="inlineStr">
         <is>
           <t>Requires authenticated session or Appium device</t>
         </is>
@@ -1564,27 +2505,27 @@
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>AnalyzingScreen</t>
         </is>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>Speech analysis pipeline (Groq + AssemblyAI)</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C26" s="10" t="inlineStr">
         <is>
           <t>Not Covered</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D26" s="10" t="inlineStr">
         <is>
           <t>src/screens/speech/AnalyzingScreen.tsx</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="E26" s="10" t="inlineStr">
         <is>
           <t>Requires authenticated session or Appium device</t>
         </is>
@@ -1618,135 +2559,135 @@
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>FillerWordsScreen / PronunciationScreen / PaceAndClarityScreen / ShareResultScreen / DailyChallengeScreen / SpeechProgressScreen</t>
         </is>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>Hardcoded/mock UI, inconsistent theming</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C28" s="10" t="inlineStr">
         <is>
           <t>Not Covered</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D28" s="10" t="inlineStr">
         <is>
           <t>src/screens/speech/</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr">
+      <c r="E28" s="10" t="inlineStr">
         <is>
           <t>Requires authenticated session or Appium device</t>
         </is>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>SpeechHistoryScreen</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>Sort + filter + search over fetched sessions (client-side)</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C29" s="10" t="inlineStr">
         <is>
           <t>Not Covered</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="D29" s="10" t="inlineStr">
         <is>
           <t>src/screens/speech/SpeechHistoryScreen.tsx</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr">
+      <c r="E29" s="10" t="inlineStr">
         <is>
           <t>Requires authenticated session or Appium device</t>
         </is>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>CompareSessionsScreen</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B30" s="10" t="inlineStr">
         <is>
           <t>Real tabular 2-session metric comparison</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C30" s="10" t="inlineStr">
         <is>
           <t>Not Covered</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="D30" s="10" t="inlineStr">
         <is>
           <t>src/screens/speech/CompareSessionsScreen.tsx</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
+      <c r="E30" s="10" t="inlineStr">
         <is>
           <t>Requires authenticated session or Appium device</t>
         </is>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>VocabularyBuilderScreen</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>Real transcript word-frequency stats</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C31" s="10" t="inlineStr">
         <is>
           <t>Not Covered</t>
         </is>
       </c>
-      <c r="D31" s="9" t="inlineStr">
+      <c r="D31" s="10" t="inlineStr">
         <is>
           <t>src/screens/speech/VocabularyBuilderScreen.tsx</t>
         </is>
       </c>
-      <c r="E31" s="9" t="inlineStr">
+      <c r="E31" s="10" t="inlineStr">
         <is>
           <t>Requires authenticated session or Appium device</t>
         </is>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>RewardsScreen / StreakCalendarScreen / LevelUpScreen</t>
         </is>
       </c>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>Gamification (Coins/XP not persisted)</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C32" s="10" t="inlineStr">
         <is>
           <t>Not Covered</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
+      <c r="D32" s="10" t="inlineStr">
         <is>
           <t>src/screens/gamification/</t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr">
+      <c r="E32" s="10" t="inlineStr">
         <is>
           <t>Requires authenticated session or Appium device</t>
         </is>
@@ -1849,7 +2790,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1905,222 +2846,222 @@
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>BUG-001</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>supabase/functions/assemblyai-transcribe/index.ts</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
         <is>
           <t>assemblyai-transcribe / assemblyai-poll Edge Functions return HTTP 404 on the live Supabase project</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="11" t="inlineStr">
         <is>
           <t>Source for both functions exists in the repo and src/services/speechService.ts:120,141 calls them by the exact same names via supabase.functions.invoke(). A direct POST to {SUPABASE_URL}/functions/v1/assemblyai-transcribe (and -poll) returns 404, while the sibling groq-analysis function returns a no</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>Live Defect</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>BUG-002</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>src/screens/auth/LoginScreen.tsx:326 (onPress={handleSubmit(onLogin)})</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>LoginScreen: submitting a completely empty form gives zero visible feedback</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>Reproduced via Selenium: clicked 'Sign In' with both fields empty. Screenshot shows no red border, no error text, no loading spinner; browser console shows no errors; no network request fired; input values remain empty strings. errors.email/errors.password are wired to render inline text (unlike Reg</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>Live Defect</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>BUG-003</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>src/screens/onboarding/WelcomeScreen.tsx</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>Welcome screen causes ~80px horizontal overflow at 1440px viewport width</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>Selenium measured document.documentElement.scrollWidth=1502 vs window.innerWidth=1422 on initial load at a 1440x1024 window. Some element on the Welcome screen exceeds the viewport width.</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>Live Defect</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>BUG-004</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>src/screens/settings/index</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>Broken barrel: SubscriptionScreen</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Exports non-existent file</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>Static Analysis</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>BUG-005</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>src/screens/profile/index</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>Broken barrel: LeaderboardScreen</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Exports non-existent file</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>Static Analysis</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>BUG-006</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>src/screens/settings/HelpScreen.tsx</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>HelpScreen unreachable</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>Built but not registered in navigator</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>Static Analysis</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G7" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -2131,7 +3072,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2169,66 +3110,66 @@
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>Client-side API key usage</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>services/speechService.ts calls the AssemblyAI REST API directly with a client-embedded key (EXPO_PUBLIC_ASSEMBLYAI_KEY) as a fallback path, alongside the proper server-side Edge Function path (assemblyai-transcribe/poll). Client-embedded keys are extractable from any web/mobile build.</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>Remove the direct-fetch fallback and route all AssemblyAI calls through the Edge Function exclusively.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Account deletion re-auth</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>DeleteAccountScreen re-authenticates via signInWithPassword before deleting — a good practice; no negative finding here, noted for completeness.</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>None — reference the pattern for other destructive flows.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>No rate-limit/backoff visible on auth forms</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>LoginScreen/RegisterScreen/ForgotPasswordScreen submit directly to Supabase on every click with no client-side debounce; relies entirely on Supabase's own rate limiting.</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>Consider a short client-side cooldown to reduce accidental duplicate submissions and email-quota exhaustion (RegisterScreen's own error handling already anticipates Supabase email rate-limit errors).</t>
         </is>
@@ -2239,7 +3180,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2580,27 +3521,27 @@
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>App-wide</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Zero aria-* attrs, zero semantic &lt;button&gt; tags — all divs with tabindex=0</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>DOM probe confirmed</t>
         </is>
       </c>
-      <c r="E13" s="10" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>Add accessibilityLabel/accessibilityRole to all Pressables</t>
         </is>
@@ -2611,7 +3552,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2649,462 +3590,462 @@
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>Button.tsx</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>src/components/Button.tsx</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
         <is>
           <t>Empty stub (3 bytes); zero imports found anywhere in src/</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>Card.tsx</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>src/components/Card.tsx</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>Empty stub (3 bytes); zero imports found</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Input.tsx</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>src/components/Input.tsx</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>Empty stub (3 bytes); zero imports found</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Avatar.tsx</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>src/components/Avatar.tsx</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Empty stub (3 bytes); zero imports found</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Badge.tsx</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>src/components/Badge.tsx</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>Empty stub (3 bytes); zero imports found</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>ScoreRing.tsx</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>src/components/ScoreRing.tsx</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>Empty stub (3 bytes); zero imports found</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>ProgressBar.tsx</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>src/components/ProgressBar.tsx</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Empty stub (3 bytes); zero imports found</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>WebScrollView.tsx</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>src/components/WebScrollView.tsx</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>Real implementation (629 bytes) but zero imports — superseded by web/index.html CSS + App.tsx runtime CSS injection</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>webScroll.ts</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>src/utils/webScroll.ts</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>webScrollStyle/webRootStyle exported but never imported</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>api.ts</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>src/lib/api.ts</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>Empty stub (3 bytes)</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>storage.ts</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>src/lib/storage.ts</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>Empty stub (3 bytes)</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>navigation.ts</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>src/types/navigation.ts</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>Empty stub (3 bytes)</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>database.ts</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>src/types/database.ts</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>Empty stub (3 bytes)</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>AuthStack.tsx</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>src/navigation/AuthStack.tsx</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>Empty stub — superseded by inline OnboardingStack in RootNavigator.tsx</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>MainTabs.tsx</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>src/navigation/MainTabs.tsx</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>Empty stub — superseded by inline MainTabs() in RootNavigator.tsx</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>ProfileStack.tsx</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>src/navigation/ProfileStack.tsx</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>Empty stub — superseded by inline ProfileStack() in RootNavigator.tsx</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>SpeechStack.tsx</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>src/navigation/SpeechStack.tsx</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>Empty stub — superseded by inline SpeechStack() in RootNavigator.tsx</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>HelpScreen.tsx</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>src/screens/settings/HelpScreen.tsx</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>Fully implemented (search+FAQ+contact) but not registered in RootNavigator.tsx — unreachable</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>test-debug.js / test-full.js / test-register.js / test-screenshot.js / test-screenshot2.js</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>repo root</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>Ad-hoc Playwright debug scripts committed at project root, not part of any structured test suite</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>dbg_*.png / screen_*.png (~3.5MB)</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>repo root</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>Debug screenshots committed to the repo root</t>
         </is>
       </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>c:Users91637VoxiraAppsrcutils</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>repo root</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>Malformed empty directory artifact from an earlier shell command</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D22" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -3115,7 +4056,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3377,7 +4318,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3415,198 +4356,198 @@
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>Duplicate/Inconsistent</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>Two sign-out implementations: ProfileScreen.tsx:60 uses authStore.signOut(); SettingsScreen.tsx:34 calls supabase.auth.signOut() directly, bypassing the Zustand store</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>See Recommendations sheet</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Duplicate/Inconsistent</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>Gamification currency naming: DailyChallengeScreen.tsx calls it 'XP'; AchievementsScreen.tsx/RewardsScreen.tsx call it 'Coins' — same underlying (unpersisted) concept, inconsistent terminology</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>See Recommendations sheet</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Duplicate/Inconsistent</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Two overlapping web-scroll CSS mechanisms: web/index.html inline &lt;style&gt; AND App.tsx:11-52 runtime-injected CSS both patch react-native-web scroll behavior; WebScrollView.tsx component was seemingly meant to replace both but is unused</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>See Recommendations sheet</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Duplicate/Inconsistent</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>HomeStack duplicate screen registrations: SpeechHomeFromSearch / SpeechDashboardFromSearch / SpeechHistoryFromSearch re-register the same Speech screens under new names purely for Search deep-links (RootNavigator.tsx:133-148)</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>See Recommendations sheet</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Duplicate/Inconsistent</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Misleading module name: src/lib/openai.ts implements the Groq wrapper (chatGroq, calls groq-analysis function) — has nothing to do with OpenAI despite the filename</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>See Recommendations sheet</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Duplicate/Inconsistent</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>Identical placeholder text reused across screens: LoginScreen.tsx and ForgotPasswordScreen.tsx both use the exact TextInput placeholder "you@email.com" for their email field. Combined with React Navigation's default stack behavior of keeping the previous screen mounted (off-screen, zero-size) rather than unmounting it on push, this makes the two inputs indistinguishable by placeholder alone while both are in the DOM — discovered because it broke an automation locator (see selenium_model/pages/base_page.py comments); would equally confuse any other placeholder-based tooling (browser autofill heuristics, other test frameworks).</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>See Recommendations sheet</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Large File</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>src/navigation/RootNavigator.tsx (352 lines) defines every stack/tab inline in one file, including two dead sub-stacks (GamificationStack, SupportStack). Recommend splitting into the (already-scaffolded-but-empty) AuthStack.tsx/MainTabs.tsx/ProfileStack.tsx/SpeechStack.tsx files, or deleting those stubs if the inline approach is intentional.</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>Split RootNavigator.tsx</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Dead Code</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>10 instances</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>See Dead Code sheet</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>Unused Files</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>21 files</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>See Unused Files sheet</t>
         </is>
@@ -3617,7 +4558,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3649,153 +4590,153 @@
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>Add testID/accessibilityLabel props to all interactive elements (currently zero exist app-wide).</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
         <is>
           <t>Blocks reliable automated testing (this suite had to fall back to text-content XPath matching) and reduces screen-reader usability for real users.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>Delete or implement the 7 empty component stubs in src/components/ (Button, Card, Input, Avatar, Badge, ScoreRing, ProgressBar) and the 4 empty navigation stack stubs.</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>Dead/empty files mislead contributors into thinking a shared component library exists; onboarding cost for new engineers.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Fix the three broken barrel-file exports (SubscriptionScreen, LeaderboardScreen, AnalysisResultScreen) referencing non-existent files.</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>Any future import of these barrels will throw a build-breaking module resolution error.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Register HelpScreen.tsx in the navigator or remove it.</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Fully-built screen is currently unreachable by users — wasted implementation effort.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Consolidate the two sign-out implementations into a single authStore.signOut() call site.</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>SettingsScreen's direct supabase.auth.signOut() call bypasses Zustand state cleanup, risking stale `session`/`user` state after logout from Settings.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>Consolidate the two overlapping web-scroll-CSS mechanisms (web/index.html + App.tsx runtime injection) into one, and either wire up or delete WebScrollView.tsx/webScroll.ts.</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>Two independent systems solving the same problem is a maintenance hazard — a future fix applied to only one will appear to silently fail.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Route AssemblyAI calls exclusively through the assemblyai-transcribe/poll Edge Functions; remove the direct-fetch client fallback that embeds the API key.</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Reduces API key exposure surface in web/mobile bundles.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>Move the 5 root-level debug Playwright scripts and ~3.5MB of debug screenshots out of version control (into this new selenium_model/ framework or .gitignore).</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>Keeps the repository root clean; this selenium_model suite is the intended structured replacement.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>Standardize gamification terminology ('XP' vs 'Coins') and persist it server-side instead of computing client-side.</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>Currently a cosmetic inconsistency; if gamification becomes a real retention feature, unpersisted state will not survive reinstall/multi-device use.</t>
         </is>
@@ -3806,7 +4747,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3970,444 +4911,6 @@
       <c r="C9" s="3" t="inlineStr">
         <is>
           <t>DEAD — defined but never used</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Exception</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Skipped</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Pass Rate %</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>API Validation</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Accessibility</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Appium</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>90.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Authentication</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Broken Links</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>E2E Flow</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Navigation</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>38</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>38</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Smoke</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>UI Validation</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>670</v>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>670</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Validation</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Vulnerability</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -20715,6 +21218,444 @@
       <c r="K308" s="5" t="inlineStr">
         <is>
           <t>C:\Users\91637\VoxiraApp\selenium_model\reports\screenshots\passed\test_ext_030_register_google_button_1785565007719.png</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Pass Rate %</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>API Validation</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Appium</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>90.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Broken Links</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>E2E Flow</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Smoke</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>670</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>670</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -67298,74 +68239,74 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
     <col width="70" customWidth="1" min="5" max="5"/>
     <col width="70" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="66" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="70" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Test #</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Test ID</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Module</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Expected</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>Actual</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>Duration (s)</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>Timestamp</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>Screenshot</t>
         </is>
@@ -67377,32 +68318,32 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>tests/test_e2e_flows.py::test_e2e_001_full_onboarding_skip_path</t>
+          <t>tests/test_appium.py::test_appium_001_app_launches_android</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>E2E Flow</t>
+          <t>Appium</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Selenium</t>
+          <t>Appium</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>E2E-001: Full onboarding Skip path: Welcome → Get Started → Skip → RegisterScreen</t>
+          <t>APPIUM-001: App launches on Android without crashing</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>RegisterScreen visible at end of flow</t>
+          <t>App is in a non-error state within 15 seconds of launch</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>RegisterScreen reached via Welcome → Get Started → Skip</t>
+          <t>app_id=com.voxira.app, app_state=4</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr">
@@ -67411,18 +68352,14 @@
         </is>
       </c>
       <c r="I2" s="5" t="n">
-        <v>9.199999999999999</v>
+        <v>5.453</v>
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 11:37:36</t>
-        </is>
-      </c>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>C:\Users\91637\VoxiraApp\selenium_model\reports\screenshots\passed\test_e2e_001_full_onboarding_skip_path_1785564455943.png</t>
-        </is>
-      </c>
+          <t>2026-08-03 00:07:46</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="n"/>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="5" t="n">
@@ -67430,32 +68367,32 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>tests/test_e2e_flows.py::test_e2e_002_sign_in_flow_welcome_to_login</t>
+          <t>tests/test_appium.py::test_appium_002_welcome_screen_renders_android</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>E2E Flow</t>
+          <t>Appium</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Selenium</t>
+          <t>Appium</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>E2E-002: Sign In flow: Welcome → Sign In → LoginScreen</t>
+          <t>APPIUM-002: WelcomeScreen renders 'Get Started Free' button on Android</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>LoginScreen 'Welcome Back' visible</t>
+          <t>'Get Started Free' text element present</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>LoginScreen rendered via Welcome → Sign In</t>
+          <t>get_started_visible=True</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
@@ -67464,18 +68401,14 @@
         </is>
       </c>
       <c r="I3" s="5" t="n">
-        <v>4.276</v>
+        <v>6.167</v>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 11:37:45</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>C:\Users\91637\VoxiraApp\selenium_model\reports\screenshots\passed\test_e2e_002_sign_in_flow_welcome_to_login_1785564465178.png</t>
-        </is>
-      </c>
+          <t>2026-08-03 00:08:13</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="n"/>
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="5" t="n">
@@ -67483,32 +68416,32 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>tests/test_e2e_flows.py::test_e2e_003_navigate_to_forgot_password_and_back</t>
+          <t>tests/test_appium.py::test_appium_003_get_started_navigates_android</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>E2E Flow</t>
+          <t>Appium</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Selenium</t>
+          <t>Appium</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>E2E-003: Welcome → Login → Forgot Password → Return to Login</t>
+          <t>APPIUM-003: Tapping 'Get Started Free' opens onboarding carousel</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>LoginScreen visible at end of chain</t>
+          <t>'Skip' element visible on Feature1Screen</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Full round-trip navigation chain completed</t>
+          <t>skip_visible=True</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
@@ -67517,18 +68450,14 @@
         </is>
       </c>
       <c r="I4" s="5" t="n">
-        <v>6.292</v>
+        <v>9.125999999999999</v>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 11:37:56</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>C:\Users\91637\VoxiraApp\selenium_model\reports\screenshots\passed\test_e2e_003_navigate_to_forgot_password_and_back_1785564476395.png</t>
-        </is>
-      </c>
+          <t>2026-08-03 00:08:42</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="n"/>
     </row>
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="5" t="n">
@@ -67536,32 +68465,32 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>tests/test_e2e_flows.py::test_e2e_004_register_to_login_crosslink</t>
+          <t>tests/test_appium.py::test_appium_004_skip_reaches_register_android</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>E2E Flow</t>
+          <t>Appium</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Selenium</t>
+          <t>Appium</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>E2E-004: Register → Sign In link → LoginScreen</t>
+          <t>APPIUM-004: Tapping Skip on carousel reaches RegisterScreen</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>LoginScreen visible after clicking Sign In from Register</t>
+          <t>'Create Account' text visible</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>LoginScreen reached from RegisterScreen Sign In link</t>
+          <t>register_visible=True</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
@@ -67570,18 +68499,14 @@
         </is>
       </c>
       <c r="I5" s="5" t="n">
-        <v>23.548</v>
+        <v>11.271</v>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 11:38:27</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>C:\Users\91637\VoxiraApp\selenium_model\reports\screenshots\passed\test_e2e_004_register_to_login_crosslink_1785564506901.png</t>
-        </is>
-      </c>
+          <t>2026-08-03 00:09:15</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n"/>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="5" t="n">
@@ -67589,32 +68514,32 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>tests/test_e2e_flows.py::test_e2e_005_validation_chain_register</t>
+          <t>tests/test_appium.py::test_appium_005_sign_in_navigates_android</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>E2E Flow</t>
+          <t>Appium</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Selenium</t>
+          <t>Appium</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>E2E-005: Register with bad data → validation errors → fix data → errors clear</t>
+          <t>APPIUM-005: Tapping 'Sign In' on WelcomeScreen opens LoginScreen</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Validation errors shown, then cleared after correction</t>
+          <t>'Welcome Back' text visible</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>bad_calls=0, errors_cleared=True</t>
+          <t>login_visible=True</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -67623,18 +68548,14 @@
         </is>
       </c>
       <c r="I6" s="5" t="n">
-        <v>33.696</v>
+        <v>9.301</v>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 11:39:18</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>C:\Users\91637\VoxiraApp\selenium_model\reports\screenshots\passed\test_e2e_005_validation_chain_register_1785564557933.png</t>
-        </is>
-      </c>
+          <t>2026-08-03 00:09:47</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n"/>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="5" t="n">
@@ -67642,32 +68563,32 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>tests/test_e2e_flows.py::test_e2e_006_forgot_password_valid_submission</t>
+          <t>tests/test_appium.py::test_appium_006_back_button_hardware_android</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>E2E Flow</t>
+          <t>Appium</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Selenium</t>
+          <t>Appium</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>E2E-006: ForgotPassword with valid email format fires recover call</t>
+          <t>APPIUM-006: Android hardware Back button returns to WelcomeScreen from Login</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>≥1 call to /auth/v1/recover after submitting valid email</t>
+          <t>'Get Started Free' visible after pressing hardware back</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>recover_calls=1</t>
+          <t>welcome_after_back=True</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -67676,18 +68597,14 @@
         </is>
       </c>
       <c r="I7" s="5" t="n">
-        <v>8.621</v>
+        <v>11.398</v>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 11:39:31</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>C:\Users\91637\VoxiraApp\selenium_model\reports\screenshots\passed\test_e2e_006_forgot_password_valid_submission_1785564571485.png</t>
-        </is>
-      </c>
+          <t>2026-08-03 00:10:23</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n"/>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="5" t="n">
@@ -67695,32 +68612,32 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>tests/test_e2e_flows.py::test_e2e_007_multiple_xss_payloads_all_blocked</t>
+          <t>tests/test_appium.py::test_appium_007_keyboard_appears_on_email_tap</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>E2E Flow</t>
+          <t>Appium</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Selenium</t>
+          <t>Appium</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>E2E-007: All 5 XSS payloads in Login email field are blocked (no alert, 0 calls)</t>
+          <t>APPIUM-007: Tapping email input on LoginScreen shows software keyboard</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>0 alerts, 0 auth calls across all payloads</t>
+          <t>Keyboard is shown after tapping email field</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>alerts=0, network_calls=0</t>
+          <t>keyboard_shown=True</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
@@ -67729,18 +68646,14 @@
         </is>
       </c>
       <c r="I8" s="5" t="n">
-        <v>87.117</v>
+        <v>12.004</v>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 11:41:04</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>C:\Users\91637\VoxiraApp\selenium_model\reports\screenshots\passed\test_e2e_007_multiple_xss_payloads_all_blocked_1785564663997.png</t>
-        </is>
-      </c>
+          <t>2026-08-03 00:10:56</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n"/>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="5" t="n">
@@ -67748,32 +68661,32 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>tests/test_e2e_flows.py::test_e2e_008_onboarding_no_errors_throughout</t>
+          <t>tests/test_appium.py::test_appium_008_typing_email_updates_field</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>E2E Flow</t>
+          <t>Appium</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Selenium</t>
+          <t>Appium</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>E2E-008: Full onboarding (Welcome→Carousel→Skip→Register) has 0 JS SEVERE errors</t>
+          <t>APPIUM-008: Typing email into LoginScreen email field updates its value</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>0 SEVERE console entries across all screens</t>
+          <t>Field contains 'test@example.com' after typing</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>0 SEVERE errors</t>
+          <t>field_value='test@example.com'</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -67782,18 +68695,14 @@
         </is>
       </c>
       <c r="I9" s="5" t="n">
-        <v>6.267</v>
+        <v>9.781000000000001</v>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 11:41:15</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>C:\Users\91637\VoxiraApp\selenium_model\reports\screenshots\passed\test_e2e_008_onboarding_no_errors_throughout_1785564675162.png</t>
-        </is>
-      </c>
+          <t>2026-08-03 00:11:31</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n"/>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="5" t="n">
@@ -67801,32 +68710,32 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>tests/test_e2e_flows.py::test_e2e_009_login_invalid_then_forgot_password</t>
+          <t>tests/test_appium.py::test_appium_009_app_does_not_crash_on_rotate_android</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>E2E Flow</t>
+          <t>Appium</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Selenium</t>
+          <t>Appium</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>E2E-009: Failed login → click Forgot Password → send reset → Return to Login</t>
+          <t>APPIUM-009: App survives screen rotation (portrait → landscape → portrait)</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>LoginScreen visible at end; total auth calls = 1 (invalid login attempt)</t>
+          <t>'Get Started Free' still visible; landscape rotation itself may be rejected by the OS since app.json declares "orientation": "portrait" — that rejection is the app correctly enforcing its own config, not a crash</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Full login→forgot_password→return flow completed</t>
+          <t>rotation_locked_by_app_config=True, app_stable_after_rotate=True</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
@@ -67835,18 +68744,14 @@
         </is>
       </c>
       <c r="I10" s="5" t="n">
-        <v>28.85</v>
+        <v>8.298999999999999</v>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 11:41:47</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>C:\Users\91637\VoxiraApp\selenium_model\reports\screenshots\passed\test_e2e_009_login_invalid_then_forgot_password_1785564707772.png</t>
-        </is>
-      </c>
+          <t>2026-08-03 00:12:02</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n"/>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="5" t="n">
@@ -67854,32 +68759,32 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>tests/test_e2e_flows.py::test_e2e_010_register_all_invalid_fields_one_by_one</t>
+          <t>tests/test_appium.py::test_appium_010_app_state_resumes_from_background</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>E2E Flow</t>
+          <t>Appium</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Selenium</t>
+          <t>Appium</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>E2E-010: Fix register fields one by one — 0 signup calls until all valid</t>
+          <t>APPIUM-010: App resumes correctly after being sent to background</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>0 calls while any field invalid; call only when all valid (submit NOT clicked for final)</t>
+          <t>WelcomeScreen visible after foreground restoration</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Stepped through field corrections; 0 calls until all valid</t>
+          <t>welcome_visible_after_background=True</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
@@ -67888,18 +68793,14 @@
         </is>
       </c>
       <c r="I11" s="5" t="n">
-        <v>11.156</v>
+        <v>12.104</v>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 11:42:04</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>C:\Users\91637\VoxiraApp\selenium_model\reports\screenshots\passed\test_e2e_010_register_all_invalid_fields_one_by_one_1785564724135.png</t>
-        </is>
-      </c>
+          <t>2026-08-03 00:12:34</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="n"/>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="5" t="n">
@@ -67907,32 +68808,32 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>tests/test_e2e_flows.py::test_e2e_011_back_navigation_consistency</t>
+          <t>tests/test_appium.py::test_appium_011_empty_login_blocked_android</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>E2E Flow</t>
+          <t>Appium</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Selenium</t>
+          <t>Appium</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>E2E-011: Navigating to BASE_URL always returns to WelcomeScreen (SPA routing)</t>
+          <t>APPIUM-011: Empty login form submission blocked on Android</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>WelcomeScreen visible when loading BASE_URL directly</t>
+          <t>Stays on LoginScreen after empty submit</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>WelcomeScreen confirmed after direct BASE_URL navigation (SPA pattern)</t>
+          <t>still_on_login=True</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -67941,18 +68842,14 @@
         </is>
       </c>
       <c r="I12" s="5" t="n">
-        <v>7.803</v>
+        <v>10.159</v>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 11:42:16</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>C:\Users\91637\VoxiraApp\selenium_model\reports\screenshots\passed\test_e2e_011_back_navigation_consistency_1785564736748.png</t>
-        </is>
-      </c>
+          <t>2026-08-03 00:13:04</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n"/>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="5" t="n">
@@ -67960,32 +68857,32 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>tests/test_e2e_flows.py::test_e2e_012_page_reload_returns_to_welcome</t>
+          <t>tests/test_appium.py::test_appium_012_register_four_fields_visible</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>E2E Flow</t>
+          <t>Appium</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Selenium</t>
+          <t>Appium</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>E2E-012: Hard-refreshing the page always renders WelcomeScreen (no URL routing)</t>
+          <t>APPIUM-012: RegisterScreen shows ≥3 EditText fields</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>WelcomeScreen visible after driver.refresh() on any screen</t>
+          <t>≥3 android.widget.EditText elements</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>WelcomeScreen shown after hard refresh</t>
+          <t>input_count=4</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
@@ -67994,18 +68891,14 @@
         </is>
       </c>
       <c r="I13" s="5" t="n">
-        <v>7.76</v>
+        <v>10.764</v>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 11:42:28</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>C:\Users\91637\VoxiraApp\selenium_model\reports\screenshots\passed\test_e2e_012_page_reload_returns_to_welcome_1785564748819.png</t>
-        </is>
-      </c>
+          <t>2026-08-03 00:13:38</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="5" t="n">
@@ -68013,32 +68906,32 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>tests/test_e2e_flows.py::test_e2e_013_three_failed_logins_no_lockout_ui</t>
+          <t>tests/test_appium.py::test_appium_013_forgot_password_navigation</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>E2E Flow</t>
+          <t>Appium</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Selenium</t>
+          <t>Appium</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>E2E-013: 3 consecutive failed login attempts — app stays functional (no client lockout)</t>
+          <t>APPIUM-013: 'Forgot Password?' navigates to ForgotPasswordScreen on Android</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>LoginScreen still interactive after 3 failures</t>
+          <t>'Forgot Password?' heading visible</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>LoginScreen remains interactive after 3 failed attempts</t>
+          <t>forgot_screen_visible=True</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
@@ -68047,18 +68940,14 @@
         </is>
       </c>
       <c r="I14" s="5" t="n">
-        <v>62.15</v>
+        <v>11.257</v>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 11:43:34</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>C:\Users\91637\VoxiraApp\selenium_model\reports\screenshots\passed\test_e2e_013_three_failed_logins_no_lockout_ui_1785564814478.png</t>
-        </is>
-      </c>
+          <t>2026-08-03 00:14:12</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n"/>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="5" t="n">
@@ -68066,32 +68955,32 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>tests/test_e2e_flows.py::test_e2e_014_register_form_clears_on_navigate_away</t>
+          <t>tests/test_appium.py::test_appium_014_password_field_is_masked</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>E2E Flow</t>
+          <t>Appium</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Selenium</t>
+          <t>Appium</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>E2E-014: Register → Login → Register again — form state is reset</t>
+          <t>APPIUM-014: Password field on LoginScreen is masked (password input type)</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>RegisterScreen has empty fields on second visit (no stale state)</t>
+          <t>EditText has password input type attribute</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>name_field_value=''</t>
+          <t>password_fields=1</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
@@ -68100,18 +68989,14 @@
         </is>
       </c>
       <c r="I15" s="5" t="n">
-        <v>40.141</v>
+        <v>8.695</v>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 11:44:19</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>C:\Users\91637\VoxiraApp\selenium_model\reports\screenshots\passed\test_e2e_014_register_form_clears_on_navigate_away_1785564859743.png</t>
-        </is>
-      </c>
+          <t>2026-08-03 00:14:43</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n"/>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="5" t="n">
@@ -68119,32 +69004,32 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>tests/test_e2e_flows.py::test_e2e_015_network_requests_stable_after_failed_login</t>
+          <t>tests/test_appium.py::test_appium_015_google_sign_in_button_present</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>E2E Flow</t>
+          <t>Appium</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Selenium</t>
+          <t>Appium</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>E2E-015: After failed login, no retry storm — call count stays at 1 for 5 seconds</t>
+          <t>APPIUM-015: 'Continue with Google' button present on Android LoginScreen</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>auth call count doesn't grow after initial 1 call</t>
+          <t>Google button element found</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>calls_4s=0, calls_7s=0</t>
+          <t>google_button=True</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
@@ -68153,18 +69038,14 @@
         </is>
       </c>
       <c r="I16" s="5" t="n">
-        <v>28.171</v>
+        <v>8.617000000000001</v>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 11:44:52</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>C:\Users\91637\VoxiraApp\selenium_model\reports\screenshots\passed\test_e2e_015_network_requests_stable_after_failed_login_1785564892613.png</t>
-        </is>
-      </c>
+          <t>2026-08-03 00:15:13</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n"/>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="5" t="n">
@@ -68172,32 +69053,32 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>tests/test_e2e_flows.py::test_e2e_016_tab_bar_shown_only_when_authenticated</t>
+          <t>tests/test_appium.py::test_appium_016_swipe_up_on_register_screen</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>E2E Flow</t>
+          <t>Appium</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Selenium</t>
+          <t>Appium</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>E2E-016: Tab bar is NOT visible on unauthenticated screens</t>
+          <t>APPIUM-016: Swipe up on RegisterScreen scrolls without crashing</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Home/Speech/Profile tabs absent on WelcomeScreen and LoginScreen</t>
+          <t>App remains stable after swipe gesture</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>tabs_on_welcome=False, tabs_on_login=False</t>
+          <t>screen_stable_after_swipe=True</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -68206,18 +69087,202 @@
         </is>
       </c>
       <c r="I17" s="5" t="n">
-        <v>20.083</v>
+        <v>13.593</v>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 11:45:17</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>C:\Users\91637\VoxiraApp\selenium_model\reports\screenshots\passed\test_e2e_016_tab_bar_shown_only_when_authenticated_1785564917461.png</t>
-        </is>
-      </c>
+          <t>2026-08-03 00:15:49</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>tests/test_appium.py::test_appium_017_tab_bar_tabs_count</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Appium</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>Appium</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>APPIUM-017: Bottom tab bar shows 5 tabs after login (authenticated)</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>5 tab labels visible (Home, Speech, Goals, Earn, Profile)</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="n"/>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="I18" s="9" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-03 00:16:11</t>
+        </is>
+      </c>
+      <c r="K18" s="9" t="n"/>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>tests/test_appium.py::test_appium_018_mic_permission_dialog_android</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Appium</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Appium</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>APPIUM-018: Mic permission dialog can be accepted on Android</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>Permission dialog appears and can be accepted without crash</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="n"/>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="I19" s="9" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="J19" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-03 00:16:33</t>
+        </is>
+      </c>
+      <c r="K19" s="9" t="n"/>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>tests/test_appium.py::test_appium_019_app_not_in_debug_mode_production</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Appium</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Appium</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>APPIUM-019: Production build does not show Metro debug overlay</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>No 'Metro' or 'Debug' overlay text visible in production build</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>metro=False, debugger=False</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>16.338</v>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-03 00:17:09</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>tests/test_appium.py::test_appium_020_app_logo_visible_android</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Appium</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Appium</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>APPIUM-020: VOXIRA brand text visible on WelcomeScreen (Android)</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>'VOX' or 'VOXIRA' text element present on WelcomeScreen</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>brand_visible=True</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>6.194</v>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-03 00:17:37</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/selenium_model/MASTER_TEST_AUDIT_REPORT.xlsx
+++ b/selenium_model/MASTER_TEST_AUDIT_REPORT.xlsx
@@ -49,7 +49,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -93,11 +93,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
@@ -130,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -163,9 +158,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -560,7 +552,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03 00:24:01</t>
+          <t>2026-08-03 00:47:09</t>
         </is>
       </c>
     </row>
@@ -633,7 +625,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>1086</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
@@ -663,7 +655,7 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
@@ -674,7 +666,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -706,7 +698,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>18/20 (90.0%)</t>
+          <t>20/20 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -1911,81 +1903,81 @@
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>GoalSelectionScreen</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>Multi-select onboarding goals, saved to Supabase</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>Not Covered</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>src/screens/onboarding/GoalSelectionScreen.tsx</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>Requires authenticated session or Appium device</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>ExperienceLevelScreen</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Single-select skill level, saved to Supabase</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>Not Covered</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>src/screens/onboarding/ExperienceLevelScreen.tsx</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>Requires authenticated session or Appium device</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>PermissionsScreen</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Mic/notification permission requests</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Not Covered</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>src/screens/onboarding/PermissionsScreen.tsx</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Requires authenticated session or Appium device</t>
         </is>
@@ -2073,108 +2065,108 @@
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>DeleteAccountScreen</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>Multi-step account deletion wizard</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Not Covered</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>src/screens/auth/DeleteAccountScreen.tsx</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>Requires authenticated session or Appium device</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>DashboardScreen</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Stat cards, recent sessions, pull-to-refresh</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>Not Covered</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>src/screens/home/DashboardScreen.tsx</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>Requires authenticated session or Appium device</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>SearchScreen</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>Client-side text+category filter (static array)</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>Not Covered</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>src/screens/home/SearchScreen.tsx</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Requires authenticated session or Appium device</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>DailyGoalScreen</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Stepper form for daily speech target + reminders</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>Not Covered</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>src/screens/home/DailyGoalScreen.tsx</t>
         </is>
       </c>
-      <c r="E13" s="10" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>Requires authenticated session or Appium device</t>
         </is>
@@ -2208,27 +2200,27 @@
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>TopicDetailScreen</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Static topic content viewer</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>Not Covered</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>src/screens/home/TopicDetailScreen.tsx</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>Requires authenticated session or Appium device</t>
         </is>
@@ -2262,81 +2254,81 @@
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>EditProfileScreen</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>Profile form + avatar upload to Supabase Storage</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>Not Covered</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>src/screens/profile/EditProfileScreen.tsx</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>Requires authenticated session or Appium device</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>ProgressOverviewScreen</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>Stat aggregation from session history</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>Not Covered</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>src/screens/profile/ProgressOverviewScreen.tsx</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>Requires authenticated session or Appium device</t>
         </is>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>AchievementsScreen</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>12 hardcoded achievements evaluated against real session data</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>Not Covered</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>src/screens/profile/AchievementsScreen.tsx</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>Requires authenticated session or Appium device</t>
         </is>
@@ -2370,54 +2362,54 @@
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>NotificationSettingsScreen</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>6 notification toggles + reminder time</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>Not Covered</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>src/screens/settings/NotificationSettingsScreen.tsx</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>Requires authenticated session or Appium device</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>PrivacyPolicyScreen</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>Static accordion content</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>Not Covered</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>src/screens/settings/PrivacyPolicyScreen.tsx</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>Requires authenticated session or Appium device</t>
         </is>
@@ -2451,27 +2443,27 @@
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>FAQScreen / TutorialScreen / WhatsNewScreen</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>Static support content</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>Not Covered</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>src/screens/support/</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>Requires authenticated session or Appium device</t>
         </is>
@@ -2505,27 +2497,27 @@
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>AnalyzingScreen</t>
         </is>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>Speech analysis pipeline (Groq + AssemblyAI)</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>Not Covered</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>src/screens/speech/AnalyzingScreen.tsx</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>Requires authenticated session or Appium device</t>
         </is>
@@ -2559,135 +2551,135 @@
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>FillerWordsScreen / PronunciationScreen / PaceAndClarityScreen / ShareResultScreen / DailyChallengeScreen / SpeechProgressScreen</t>
         </is>
       </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>Hardcoded/mock UI, inconsistent theming</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>Not Covered</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>src/screens/speech/</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr">
+      <c r="E28" s="9" t="inlineStr">
         <is>
           <t>Requires authenticated session or Appium device</t>
         </is>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>SpeechHistoryScreen</t>
         </is>
       </c>
-      <c r="B29" s="10" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>Sort + filter + search over fetched sessions (client-side)</t>
         </is>
       </c>
-      <c r="C29" s="10" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>Not Covered</t>
         </is>
       </c>
-      <c r="D29" s="10" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>src/screens/speech/SpeechHistoryScreen.tsx</t>
         </is>
       </c>
-      <c r="E29" s="10" t="inlineStr">
+      <c r="E29" s="9" t="inlineStr">
         <is>
           <t>Requires authenticated session or Appium device</t>
         </is>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>CompareSessionsScreen</t>
         </is>
       </c>
-      <c r="B30" s="10" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>Real tabular 2-session metric comparison</t>
         </is>
       </c>
-      <c r="C30" s="10" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>Not Covered</t>
         </is>
       </c>
-      <c r="D30" s="10" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>src/screens/speech/CompareSessionsScreen.tsx</t>
         </is>
       </c>
-      <c r="E30" s="10" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>Requires authenticated session or Appium device</t>
         </is>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>VocabularyBuilderScreen</t>
         </is>
       </c>
-      <c r="B31" s="10" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>Real transcript word-frequency stats</t>
         </is>
       </c>
-      <c r="C31" s="10" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>Not Covered</t>
         </is>
       </c>
-      <c r="D31" s="10" t="inlineStr">
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>src/screens/speech/VocabularyBuilderScreen.tsx</t>
         </is>
       </c>
-      <c r="E31" s="10" t="inlineStr">
+      <c r="E31" s="9" t="inlineStr">
         <is>
           <t>Requires authenticated session or Appium device</t>
         </is>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>RewardsScreen / StreakCalendarScreen / LevelUpScreen</t>
         </is>
       </c>
-      <c r="B32" s="10" t="inlineStr">
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>Gamification (Coins/XP not persisted)</t>
         </is>
       </c>
-      <c r="C32" s="10" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>Not Covered</t>
         </is>
       </c>
-      <c r="D32" s="10" t="inlineStr">
+      <c r="D32" s="9" t="inlineStr">
         <is>
           <t>src/screens/gamification/</t>
         </is>
       </c>
-      <c r="E32" s="10" t="inlineStr">
+      <c r="E32" s="9" t="inlineStr">
         <is>
           <t>Requires authenticated session or Appium device</t>
         </is>
@@ -2846,222 +2838,222 @@
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>BUG-001</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>supabase/functions/assemblyai-transcribe/index.ts</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>assemblyai-transcribe / assemblyai-poll Edge Functions return HTTP 404 on the live Supabase project</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>Source for both functions exists in the repo and src/services/speechService.ts:120,141 calls them by the exact same names via supabase.functions.invoke(). A direct POST to {SUPABASE_URL}/functions/v1/assemblyai-transcribe (and -poll) returns 404, while the sibling groq-analysis function returns a no</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>Live Defect</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>BUG-002</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>src/screens/auth/LoginScreen.tsx:326 (onPress={handleSubmit(onLogin)})</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>LoginScreen: submitting a completely empty form gives zero visible feedback</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>Reproduced via Selenium: clicked 'Sign In' with both fields empty. Screenshot shows no red border, no error text, no loading spinner; browser console shows no errors; no network request fired; input values remain empty strings. errors.email/errors.password are wired to render inline text (unlike Reg</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>Live Defect</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>BUG-003</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>src/screens/onboarding/WelcomeScreen.tsx</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>Welcome screen causes ~80px horizontal overflow at 1440px viewport width</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>Selenium measured document.documentElement.scrollWidth=1502 vs window.innerWidth=1422 on initial load at a 1440x1024 window. Some element on the Welcome screen exceeds the viewport width.</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>Live Defect</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>BUG-004</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>src/screens/settings/index</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Broken barrel: SubscriptionScreen</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>Exports non-existent file</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>Static Analysis</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>BUG-005</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>src/screens/profile/index</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>Broken barrel: LeaderboardScreen</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>Exports non-existent file</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>Static Analysis</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>BUG-006</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>src/screens/settings/HelpScreen.tsx</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>HelpScreen unreachable</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>Built but not registered in navigator</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>Static Analysis</t>
         </is>
       </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -3110,66 +3102,66 @@
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>Client-side API key usage</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>services/speechService.ts calls the AssemblyAI REST API directly with a client-embedded key (EXPO_PUBLIC_ASSEMBLYAI_KEY) as a fallback path, alongside the proper server-side Edge Function path (assemblyai-transcribe/poll). Client-embedded keys are extractable from any web/mobile build.</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t>Remove the direct-fetch fallback and route all AssemblyAI calls through the Edge Function exclusively.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>Account deletion re-auth</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>DeleteAccountScreen re-authenticates via signInWithPassword before deleting — a good practice; no negative finding here, noted for completeness.</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>None — reference the pattern for other destructive flows.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>No rate-limit/backoff visible on auth forms</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>LoginScreen/RegisterScreen/ForgotPasswordScreen submit directly to Supabase on every click with no client-side debounce; relies entirely on Supabase's own rate limiting.</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>Consider a short client-side cooldown to reduce accidental duplicate submissions and email-quota exhaustion (RegisterScreen's own error handling already anticipates Supabase email rate-limit errors).</t>
         </is>
@@ -3521,27 +3513,27 @@
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>App-wide</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>Zero aria-* attrs, zero semantic &lt;button&gt; tags — all divs with tabindex=0</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>DOM probe confirmed</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="10" t="inlineStr">
         <is>
           <t>Add accessibilityLabel/accessibilityRole to all Pressables</t>
         </is>
@@ -3590,462 +3582,462 @@
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>Button.tsx</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>src/components/Button.tsx</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>Empty stub (3 bytes); zero imports found anywhere in src/</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Card.tsx</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>src/components/Card.tsx</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>Empty stub (3 bytes); zero imports found</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Input.tsx</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>src/components/Input.tsx</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Empty stub (3 bytes); zero imports found</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Avatar.tsx</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>src/components/Avatar.tsx</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>Empty stub (3 bytes); zero imports found</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Badge.tsx</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>src/components/Badge.tsx</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Empty stub (3 bytes); zero imports found</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>ScoreRing.tsx</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>src/components/ScoreRing.tsx</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>Empty stub (3 bytes); zero imports found</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>ProgressBar.tsx</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>src/components/ProgressBar.tsx</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Empty stub (3 bytes); zero imports found</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>WebScrollView.tsx</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>src/components/WebScrollView.tsx</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>Real implementation (629 bytes) but zero imports — superseded by web/index.html CSS + App.tsx runtime CSS injection</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>webScroll.ts</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>src/utils/webScroll.ts</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>webScrollStyle/webRootStyle exported but never imported</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>api.ts</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>src/lib/api.ts</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>Empty stub (3 bytes)</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>storage.ts</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>src/lib/storage.ts</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>Empty stub (3 bytes)</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>navigation.ts</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>src/types/navigation.ts</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>Empty stub (3 bytes)</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>database.ts</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>src/types/database.ts</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>Empty stub (3 bytes)</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>AuthStack.tsx</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>src/navigation/AuthStack.tsx</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>Empty stub — superseded by inline OnboardingStack in RootNavigator.tsx</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>MainTabs.tsx</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>src/navigation/MainTabs.tsx</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>Empty stub — superseded by inline MainTabs() in RootNavigator.tsx</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>ProfileStack.tsx</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>src/navigation/ProfileStack.tsx</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>Empty stub — superseded by inline ProfileStack() in RootNavigator.tsx</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>SpeechStack.tsx</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>src/navigation/SpeechStack.tsx</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>Empty stub — superseded by inline SpeechStack() in RootNavigator.tsx</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>HelpScreen.tsx</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>src/screens/settings/HelpScreen.tsx</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>Fully implemented (search+FAQ+contact) but not registered in RootNavigator.tsx — unreachable</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>test-debug.js / test-full.js / test-register.js / test-screenshot.js / test-screenshot2.js</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>repo root</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>Ad-hoc Playwright debug scripts committed at project root, not part of any structured test suite</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>dbg_*.png / screen_*.png (~3.5MB)</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>repo root</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>Debug screenshots committed to the repo root</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>c:Users91637VoxiraAppsrcutils</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>repo root</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>Malformed empty directory artifact from an earlier shell command</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -4356,198 +4348,198 @@
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>Duplicate/Inconsistent</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>Two sign-out implementations: ProfileScreen.tsx:60 uses authStore.signOut(); SettingsScreen.tsx:34 calls supabase.auth.signOut() directly, bypassing the Zustand store</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t>See Recommendations sheet</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>Duplicate/Inconsistent</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>Gamification currency naming: DailyChallengeScreen.tsx calls it 'XP'; AchievementsScreen.tsx/RewardsScreen.tsx call it 'Coins' — same underlying (unpersisted) concept, inconsistent terminology</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>See Recommendations sheet</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Duplicate/Inconsistent</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>Two overlapping web-scroll CSS mechanisms: web/index.html inline &lt;style&gt; AND App.tsx:11-52 runtime-injected CSS both patch react-native-web scroll behavior; WebScrollView.tsx component was seemingly meant to replace both but is unused</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>See Recommendations sheet</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Duplicate/Inconsistent</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>HomeStack duplicate screen registrations: SpeechHomeFromSearch / SpeechDashboardFromSearch / SpeechHistoryFromSearch re-register the same Speech screens under new names purely for Search deep-links (RootNavigator.tsx:133-148)</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>See Recommendations sheet</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Duplicate/Inconsistent</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Misleading module name: src/lib/openai.ts implements the Groq wrapper (chatGroq, calls groq-analysis function) — has nothing to do with OpenAI despite the filename</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>See Recommendations sheet</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Duplicate/Inconsistent</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Identical placeholder text reused across screens: LoginScreen.tsx and ForgotPasswordScreen.tsx both use the exact TextInput placeholder "you@email.com" for their email field. Combined with React Navigation's default stack behavior of keeping the previous screen mounted (off-screen, zero-size) rather than unmounting it on push, this makes the two inputs indistinguishable by placeholder alone while both are in the DOM — discovered because it broke an automation locator (see selenium_model/pages/base_page.py comments); would equally confuse any other placeholder-based tooling (browser autofill heuristics, other test frameworks).</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>See Recommendations sheet</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Large File</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>src/navigation/RootNavigator.tsx (352 lines) defines every stack/tab inline in one file, including two dead sub-stacks (GamificationStack, SupportStack). Recommend splitting into the (already-scaffolded-but-empty) AuthStack.tsx/MainTabs.tsx/ProfileStack.tsx/SpeechStack.tsx files, or deleting those stubs if the inline approach is intentional.</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>Split RootNavigator.tsx</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Dead Code</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>10 instances</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>See Dead Code sheet</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Unused Files</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>21 files</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>See Unused Files sheet</t>
         </is>
@@ -4590,153 +4582,153 @@
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>Add testID/accessibilityLabel props to all interactive elements (currently zero exist app-wide).</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>Blocks reliable automated testing (this suite had to fall back to text-content XPath matching) and reduces screen-reader usability for real users.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>Delete or implement the 7 empty component stubs in src/components/ (Button, Card, Input, Avatar, Badge, ScoreRing, ProgressBar) and the 4 empty navigation stack stubs.</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>Dead/empty files mislead contributors into thinking a shared component library exists; onboarding cost for new engineers.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Fix the three broken barrel-file exports (SubscriptionScreen, LeaderboardScreen, AnalysisResultScreen) referencing non-existent files.</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Any future import of these barrels will throw a build-breaking module resolution error.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Register HelpScreen.tsx in the navigator or remove it.</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>Fully-built screen is currently unreachable by users — wasted implementation effort.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Consolidate the two sign-out implementations into a single authStore.signOut() call site.</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>SettingsScreen's direct supabase.auth.signOut() call bypasses Zustand state cleanup, risking stale `session`/`user` state after logout from Settings.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Consolidate the two overlapping web-scroll-CSS mechanisms (web/index.html + App.tsx runtime injection) into one, and either wire up or delete WebScrollView.tsx/webScroll.ts.</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>Two independent systems solving the same problem is a maintenance hazard — a future fix applied to only one will appear to silently fail.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>Route AssemblyAI calls exclusively through the assemblyai-transcribe/poll Edge Functions; remove the direct-fetch client fallback that embeds the API key.</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Reduces API key exposure surface in web/mobile bundles.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>Move the 5 root-level debug Playwright scripts and ~3.5MB of debug screenshots out of version control (into this new selenium_model/ framework or .gitignore).</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>Keeps the repository root clean; this selenium_model suite is the intended structured replacement.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>Standardize gamification terminology ('XP' vs 'Coins') and persist it server-side instead of computing client-side.</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>Currently a cosmetic inconsistency; if gamification becomes a real retention feature, unpersisted state will not survive reinstall/multi-device use.</t>
         </is>
@@ -21345,7 +21337,7 @@
         <v>20</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0</v>
@@ -21354,11 +21346,11 @@
         <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -68249,7 +68241,7 @@
     <col width="70" customWidth="1" min="5" max="5"/>
     <col width="70" customWidth="1" min="6" max="6"/>
     <col width="66" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
@@ -68352,11 +68344,11 @@
         </is>
       </c>
       <c r="I2" s="5" t="n">
-        <v>5.453</v>
+        <v>5.436</v>
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>2026-08-03 00:07:46</t>
+          <t>2026-08-03 00:35:22</t>
         </is>
       </c>
       <c r="K2" s="5" t="n"/>
@@ -68401,11 +68393,11 @@
         </is>
       </c>
       <c r="I3" s="5" t="n">
-        <v>6.167</v>
+        <v>6.201</v>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>2026-08-03 00:08:13</t>
+          <t>2026-08-03 00:35:48</t>
         </is>
       </c>
       <c r="K3" s="5" t="n"/>
@@ -68450,11 +68442,11 @@
         </is>
       </c>
       <c r="I4" s="5" t="n">
-        <v>9.125999999999999</v>
+        <v>9.164999999999999</v>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>2026-08-03 00:08:42</t>
+          <t>2026-08-03 00:36:19</t>
         </is>
       </c>
       <c r="K4" s="5" t="n"/>
@@ -68499,11 +68491,11 @@
         </is>
       </c>
       <c r="I5" s="5" t="n">
-        <v>11.271</v>
+        <v>11.358</v>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>2026-08-03 00:09:15</t>
+          <t>2026-08-03 00:36:51</t>
         </is>
       </c>
       <c r="K5" s="5" t="n"/>
@@ -68548,11 +68540,11 @@
         </is>
       </c>
       <c r="I6" s="5" t="n">
-        <v>9.301</v>
+        <v>8.659000000000001</v>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>2026-08-03 00:09:47</t>
+          <t>2026-08-03 00:37:21</t>
         </is>
       </c>
       <c r="K6" s="5" t="n"/>
@@ -68597,11 +68589,11 @@
         </is>
       </c>
       <c r="I7" s="5" t="n">
-        <v>11.398</v>
+        <v>10.803</v>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>2026-08-03 00:10:23</t>
+          <t>2026-08-03 00:37:54</t>
         </is>
       </c>
       <c r="K7" s="5" t="n"/>
@@ -68646,11 +68638,11 @@
         </is>
       </c>
       <c r="I8" s="5" t="n">
-        <v>12.004</v>
+        <v>12.191</v>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>2026-08-03 00:10:56</t>
+          <t>2026-08-03 00:38:26</t>
         </is>
       </c>
       <c r="K8" s="5" t="n"/>
@@ -68695,11 +68687,11 @@
         </is>
       </c>
       <c r="I9" s="5" t="n">
-        <v>9.781000000000001</v>
+        <v>9.837</v>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>2026-08-03 00:11:31</t>
+          <t>2026-08-03 00:38:58</t>
         </is>
       </c>
       <c r="K9" s="5" t="n"/>
@@ -68744,11 +68736,11 @@
         </is>
       </c>
       <c r="I10" s="5" t="n">
-        <v>8.298999999999999</v>
+        <v>8.382</v>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>2026-08-03 00:12:02</t>
+          <t>2026-08-03 00:39:28</t>
         </is>
       </c>
       <c r="K10" s="5" t="n"/>
@@ -68793,11 +68785,11 @@
         </is>
       </c>
       <c r="I11" s="5" t="n">
-        <v>12.104</v>
+        <v>11.993</v>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>2026-08-03 00:12:34</t>
+          <t>2026-08-03 00:40:01</t>
         </is>
       </c>
       <c r="K11" s="5" t="n"/>
@@ -68842,11 +68834,11 @@
         </is>
       </c>
       <c r="I12" s="5" t="n">
-        <v>10.159</v>
+        <v>10.003</v>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>2026-08-03 00:13:04</t>
+          <t>2026-08-03 00:40:32</t>
         </is>
       </c>
       <c r="K12" s="5" t="n"/>
@@ -68891,11 +68883,11 @@
         </is>
       </c>
       <c r="I13" s="5" t="n">
-        <v>10.764</v>
+        <v>11.546</v>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>2026-08-03 00:13:38</t>
+          <t>2026-08-03 00:41:04</t>
         </is>
       </c>
       <c r="K13" s="5" t="n"/>
@@ -68940,11 +68932,11 @@
         </is>
       </c>
       <c r="I14" s="5" t="n">
-        <v>11.257</v>
+        <v>10.947</v>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>2026-08-03 00:14:12</t>
+          <t>2026-08-03 00:41:36</t>
         </is>
       </c>
       <c r="K14" s="5" t="n"/>
@@ -68989,11 +68981,11 @@
         </is>
       </c>
       <c r="I15" s="5" t="n">
-        <v>8.695</v>
+        <v>8.532999999999999</v>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>2026-08-03 00:14:43</t>
+          <t>2026-08-03 00:42:05</t>
         </is>
       </c>
       <c r="K15" s="5" t="n"/>
@@ -69038,11 +69030,11 @@
         </is>
       </c>
       <c r="I16" s="5" t="n">
-        <v>8.617000000000001</v>
+        <v>8.66</v>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>2026-08-03 00:15:13</t>
+          <t>2026-08-03 00:42:36</t>
         </is>
       </c>
       <c r="K16" s="5" t="n"/>
@@ -69087,104 +69079,112 @@
         </is>
       </c>
       <c r="I17" s="5" t="n">
-        <v>13.593</v>
+        <v>12.881</v>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>2026-08-03 00:15:49</t>
+          <t>2026-08-03 00:43:10</t>
         </is>
       </c>
       <c r="K17" s="5" t="n"/>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="9" t="n">
+      <c r="A18" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>tests/test_appium.py::test_appium_017_tab_bar_tabs_count</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Appium</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Appium</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>APPIUM-017: Bottom tab bar shows 5 tabs after login (authenticated)</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>5 tab labels visible (Home, Speech, Goals, Earn, Profile)</t>
         </is>
       </c>
-      <c r="G18" s="9" t="n"/>
-      <c r="H18" s="9" t="inlineStr">
-        <is>
-          <t>Skipped</t>
-        </is>
-      </c>
-      <c r="I18" s="9" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="J18" s="9" t="inlineStr">
-        <is>
-          <t>2026-08-03 00:16:11</t>
-        </is>
-      </c>
-      <c r="K18" s="9" t="n"/>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>visible_tabs=['Home', 'Speech', 'Goals', 'Earn', 'Profile']</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>16.769</v>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-03 00:43:47</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n"/>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="9" t="n">
+      <c r="A19" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>tests/test_appium.py::test_appium_018_mic_permission_dialog_android</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Appium</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Appium</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>APPIUM-018: Mic permission dialog can be accepted on Android</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr">
-        <is>
-          <t>Permission dialog appears and can be accepted without crash</t>
-        </is>
-      </c>
-      <c r="G19" s="9" t="n"/>
-      <c r="H19" s="9" t="inlineStr">
-        <is>
-          <t>Skipped</t>
-        </is>
-      </c>
-      <c r="I19" s="9" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="J19" s="9" t="inlineStr">
-        <is>
-          <t>2026-08-03 00:16:33</t>
-        </is>
-      </c>
-      <c r="K19" s="9" t="n"/>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Permission dialog appears when requesting RECORD_AUDIO and can be accepted</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>dialog_shown=True, accepted=True</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>20.46</v>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-03 00:44:27</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n"/>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="5" t="n">
@@ -69226,11 +69226,11 @@
         </is>
       </c>
       <c r="I20" s="5" t="n">
-        <v>16.338</v>
+        <v>16.322</v>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>2026-08-03 00:17:09</t>
+          <t>2026-08-03 00:45:03</t>
         </is>
       </c>
       <c r="K20" s="5" t="n"/>
@@ -69275,11 +69275,11 @@
         </is>
       </c>
       <c r="I21" s="5" t="n">
-        <v>6.194</v>
+        <v>6.203</v>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>2026-08-03 00:17:37</t>
+          <t>2026-08-03 00:45:29</t>
         </is>
       </c>
       <c r="K21" s="5" t="n"/>

--- a/selenium_model/MASTER_TEST_AUDIT_REPORT.xlsx
+++ b/selenium_model/MASTER_TEST_AUDIT_REPORT.xlsx
@@ -552,7 +552,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03 00:47:09</t>
+          <t>2026-08-03 01:36:38</t>
         </is>
       </c>
     </row>

--- a/selenium_model/MASTER_TEST_AUDIT_REPORT.xlsx
+++ b/selenium_model/MASTER_TEST_AUDIT_REPORT.xlsx
@@ -552,7 +552,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03 01:36:38</t>
+          <t>2026-08-03 14:05:57</t>
         </is>
       </c>
     </row>
